--- a/data/processed/metricas_train_ml_clusters.xlsx
+++ b/data/processed/metricas_train_ml_clusters.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,20 +441,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>best_params</t>
+          <t>r2</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>r2</t>
+          <t>rmse</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>rmse</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>mape_pct</t>
         </is>
@@ -463,157 +458,379 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>df_rec_peso_pnd25_gauss_svm_clusters</t>
+          <t>df_rec_peso_pnd25_gauss_kmeans_clusters</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>xgboost</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>{'learning_rate': 0.05, 'max_depth': 5, 'n_estimators': 150}</t>
-        </is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.1309558518800518</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3240892810488641</v>
+        <v>6.175410462134983</v>
       </c>
       <c r="E2" t="n">
-        <v>5.506560637832867</v>
-      </c>
-      <c r="F2" t="n">
-        <v>20.80123307661346</v>
+        <v>24.7011080397822</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>df_rec_peso_pnd25_gauss_gmm_clusters</t>
+          <t>df_rec_peso_pnd25_gauss_kmeans_clusters</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>xgboost</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>{'learning_rate': 0.05, 'max_depth': 5, 'n_estimators': 150}</t>
-        </is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1196391179292497</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2884854496593195</v>
+        <v>6.215488652515868</v>
       </c>
       <c r="E3" t="n">
-        <v>5.528177441146926</v>
-      </c>
-      <c r="F3" t="n">
-        <v>21.65299119676346</v>
+        <v>25.00132547690387</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>df_rec_peso_pnd25_gauss_svm_clusters</t>
+          <t>df_rec_peso_pnd25_gauss_kmeans_clusters</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>knn</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>{'n_neighbors': 15, 'p': 1, 'weights': 'distance'}</t>
-        </is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1130419180351452</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2387924109994137</v>
+        <v>6.238733828721218</v>
       </c>
       <c r="E4" t="n">
-        <v>5.843691947020183</v>
-      </c>
-      <c r="F4" t="n">
-        <v>22.44414911928441</v>
+        <v>25.06990444596258</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>df_rec_peso_pnd25_gauss_kmeans_clusters</t>
+          <t>df_rec_peso_pnd25_gauss_gmm_clusters</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>xgboost</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>{'learning_rate': 0.05, 'max_depth': 5, 'n_estimators': 150}</t>
-        </is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.1008002698922752</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2238485183305408</v>
+        <v>6.281639276670462</v>
       </c>
       <c r="E5" t="n">
-        <v>6.125706474747565</v>
-      </c>
-      <c r="F5" t="n">
-        <v>21.09160707991472</v>
+        <v>25.31322068391253</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>df_rec_peso_pnd25_gauss_gmm_clusters</t>
+          <t>df_rec_peso_pnd25_gauss_kmeans_clusters</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>knn</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>{'n_neighbors': 15, 'p': 1, 'weights': 'distance'}</t>
-        </is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.09325878289194489</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1817183863900159</v>
+        <v>6.30792597689947</v>
       </c>
       <c r="E6" t="n">
-        <v>5.928454321136599</v>
-      </c>
-      <c r="F6" t="n">
-        <v>23.14082221334681</v>
+        <v>24.32770039319421</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>df_rec_peso_pnd25_gauss_gmm_clusters</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.08818410302520763</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6.325552859499916</v>
+      </c>
+      <c r="E7" t="n">
+        <v>24.82201573570025</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>df_rec_peso_pnd25_gauss_svm_clusters</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.08055933516468428</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.351945502405423</v>
+      </c>
+      <c r="E8" t="n">
+        <v>26.72637106485916</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>df_rec_peso_pnd25_gauss_kmeans_clusters</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>knn</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>{'n_neighbors': 15, 'p': 1, 'weights': 'distance'}</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.08961471940433352</v>
-      </c>
-      <c r="E7" t="n">
-        <v>6.634306795925936</v>
-      </c>
-      <c r="F7" t="n">
-        <v>22.48861000334944</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.07565081649084393</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.368878156407486</v>
+      </c>
+      <c r="E9" t="n">
+        <v>26.82281784236775</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>df_rec_peso_pnd25_gauss_gmm_clusters</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0731596582798234</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.377454573187787</v>
+      </c>
+      <c r="E10" t="n">
+        <v>25.29706211916635</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>df_rec_peso_pnd25_gauss_svm_clusters</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.06047323075379596</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.420952967559252</v>
+      </c>
+      <c r="E11" t="n">
+        <v>27.52923314693784</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>df_rec_peso_pnd25_gauss_gmm_clusters</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.05175607580768393</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6.450671763841867</v>
+      </c>
+      <c r="E12" t="n">
+        <v>25.58707182558125</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>df_rec_peso_pnd25_gauss_svm_clusters</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.03424727166407271</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6.509953423308013</v>
+      </c>
+      <c r="E13" t="n">
+        <v>26.99018546380082</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>df_rec_peso_pnd25_gauss_kmeans_clusters</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SVR</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.03113863197388322</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6.520422376680416</v>
+      </c>
+      <c r="E14" t="n">
+        <v>23.53577662981523</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>df_rec_peso_pnd25_gauss_gmm_clusters</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.02581703607260899</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6.538304984703526</v>
+      </c>
+      <c r="E15" t="n">
+        <v>25.07847188934728</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>df_rec_peso_pnd25_gauss_svm_clusters</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.00945733506387525</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.592976118764669</v>
+      </c>
+      <c r="E16" t="n">
+        <v>28.24403917889448</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>df_rec_peso_pnd25_gauss_svm_clusters</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.00918532867563826</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6.593881283473084</v>
+      </c>
+      <c r="E17" t="n">
+        <v>27.0638548326743</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>df_rec_peso_pnd25_gauss_gmm_clusters</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SVR</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.05391494478144221</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6.800607200490215</v>
+      </c>
+      <c r="E18" t="n">
+        <v>26.1735161406325</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>df_rec_peso_pnd25_gauss_svm_clusters</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SVR</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.07397054545568471</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6.865008744784668</v>
+      </c>
+      <c r="E19" t="n">
+        <v>27.02984276811979</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/metricas_train_ml_clusters.xlsx
+++ b/data/processed/metricas_train_ml_clusters.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,15 +441,20 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>best_params</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>r2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>rmse</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>mape_pct</t>
         </is>
@@ -458,85 +463,105 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>df_rec_peso_pnd25_gauss_kmeans_clusters</t>
+          <t>df_rec_peso_pnd25_gauss_svm_clusters</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0.1309558518800518</v>
+          <t>xgboost</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.05, 'max_depth': 5, 'n_estimators': 150}</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>6.175410462134983</v>
+        <v>0.2538771120699223</v>
       </c>
       <c r="E2" t="n">
-        <v>24.7011080397822</v>
+        <v>5.34525450487106</v>
+      </c>
+      <c r="F2" t="n">
+        <v>21.14126463257744</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>df_rec_peso_pnd25_gauss_kmeans_clusters</t>
+          <t>df_rec_peso_pnd25_gauss_svm_clusters</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.1196391179292497</v>
+          <t>knn</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>{'n_neighbors': 15, 'p': 1, 'weights': 'distance'}</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>6.215488652515868</v>
+        <v>0.2404492481554774</v>
       </c>
       <c r="E3" t="n">
-        <v>25.00132547690387</v>
+        <v>5.393138903162464</v>
+      </c>
+      <c r="F3" t="n">
+        <v>21.14988109787189</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>df_rec_peso_pnd25_gauss_kmeans_clusters</t>
+          <t>df_rec_peso_pnd25_gauss_gmm_clusters</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.1130419180351452</v>
+          <t>xgboost</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.05, 'max_depth': 3, 'n_estimators': 300}</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>6.238733828721218</v>
+        <v>0.1682172990358377</v>
       </c>
       <c r="E4" t="n">
-        <v>25.06990444596258</v>
+        <v>5.734894534997155</v>
+      </c>
+      <c r="F4" t="n">
+        <v>21.63324786809919</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>df_rec_peso_pnd25_gauss_gmm_clusters</t>
+          <t>df_rec_peso_pnd25_gauss_kmeans_clusters</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.1008002698922752</v>
+          <t>xgboost</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 3, 'n_estimators': 150}</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>6.281639276670462</v>
+        <v>0.1673944381998869</v>
       </c>
       <c r="E5" t="n">
-        <v>25.31322068391253</v>
+        <v>5.895849069451947</v>
+      </c>
+      <c r="F5" t="n">
+        <v>21.61447900583803</v>
       </c>
     </row>
     <row r="6">
@@ -547,17 +572,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.09325878289194489</v>
+          <t>knn</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>{'n_neighbors': 15, 'p': 1, 'weights': 'distance'}</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>6.30792597689947</v>
+        <v>0.142540571012115</v>
       </c>
       <c r="E6" t="n">
-        <v>24.32770039319421</v>
+        <v>5.983199634217766</v>
+      </c>
+      <c r="F6" t="n">
+        <v>22.54975041069963</v>
       </c>
     </row>
     <row r="7">
@@ -568,269 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.08818410302520763</v>
+          <t>knn</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>{'n_neighbors': 9, 'p': 1, 'weights': 'distance'}</t>
+        </is>
       </c>
       <c r="D7" t="n">
-        <v>6.325552859499916</v>
+        <v>0.08608631167882108</v>
       </c>
       <c r="E7" t="n">
-        <v>24.82201573570025</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>df_rec_peso_pnd25_gauss_svm_clusters</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>GradientBoosting</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.08055933516468428</v>
-      </c>
-      <c r="D8" t="n">
-        <v>6.351945502405423</v>
-      </c>
-      <c r="E8" t="n">
-        <v>26.72637106485916</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>df_rec_peso_pnd25_gauss_kmeans_clusters</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.07565081649084393</v>
-      </c>
-      <c r="D9" t="n">
-        <v>6.368878156407486</v>
-      </c>
-      <c r="E9" t="n">
-        <v>26.82281784236775</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>df_rec_peso_pnd25_gauss_gmm_clusters</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>GradientBoosting</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.0731596582798234</v>
-      </c>
-      <c r="D10" t="n">
-        <v>6.377454573187787</v>
-      </c>
-      <c r="E10" t="n">
-        <v>25.29706211916635</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>df_rec_peso_pnd25_gauss_svm_clusters</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.06047323075379596</v>
-      </c>
-      <c r="D11" t="n">
-        <v>6.420952967559252</v>
-      </c>
-      <c r="E11" t="n">
-        <v>27.52923314693784</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>df_rec_peso_pnd25_gauss_gmm_clusters</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0.05175607580768393</v>
-      </c>
-      <c r="D12" t="n">
-        <v>6.450671763841867</v>
-      </c>
-      <c r="E12" t="n">
-        <v>25.58707182558125</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>df_rec_peso_pnd25_gauss_svm_clusters</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.03424727166407271</v>
-      </c>
-      <c r="D13" t="n">
-        <v>6.509953423308013</v>
-      </c>
-      <c r="E13" t="n">
-        <v>26.99018546380082</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>df_rec_peso_pnd25_gauss_kmeans_clusters</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SVR</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0.03113863197388322</v>
-      </c>
-      <c r="D14" t="n">
-        <v>6.520422376680416</v>
-      </c>
-      <c r="E14" t="n">
-        <v>23.53577662981523</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>df_rec_peso_pnd25_gauss_gmm_clusters</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0.02581703607260899</v>
-      </c>
-      <c r="D15" t="n">
-        <v>6.538304984703526</v>
-      </c>
-      <c r="E15" t="n">
-        <v>25.07847188934728</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>df_rec_peso_pnd25_gauss_svm_clusters</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0.00945733506387525</v>
-      </c>
-      <c r="D16" t="n">
-        <v>6.592976118764669</v>
-      </c>
-      <c r="E16" t="n">
-        <v>28.24403917889448</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>df_rec_peso_pnd25_gauss_svm_clusters</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0.00918532867563826</v>
-      </c>
-      <c r="D17" t="n">
-        <v>6.593881283473084</v>
-      </c>
-      <c r="E17" t="n">
-        <v>27.0638548326743</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>df_rec_peso_pnd25_gauss_gmm_clusters</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>SVR</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>-0.05391494478144221</v>
-      </c>
-      <c r="D18" t="n">
-        <v>6.800607200490215</v>
-      </c>
-      <c r="E18" t="n">
-        <v>26.1735161406325</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>df_rec_peso_pnd25_gauss_svm_clusters</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>SVR</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>-0.07397054545568471</v>
-      </c>
-      <c r="D19" t="n">
-        <v>6.865008744784668</v>
-      </c>
-      <c r="E19" t="n">
-        <v>27.02984276811979</v>
+        <v>6.01136481080971</v>
+      </c>
+      <c r="F7" t="n">
+        <v>24.22139557709724</v>
       </c>
     </row>
   </sheetData>
